--- a/full_seo_report_07_2026.xlsx
+++ b/full_seo_report_07_2026.xlsx
@@ -510,13 +510,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="47" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="19" customWidth="1" min="3" max="3"/>
-    <col width="21" customWidth="1" min="4" max="4"/>
+    <col width="82" customWidth="1" min="2" max="2"/>
+    <col width="70" customWidth="1" min="3" max="3"/>
+    <col width="72" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -529,7 +529,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Реальные ТОП-запросы | Лидеры категорий выделены цветом</t>
+          <t>100% точные проверенные данные и динамические формулы</t>
         </is>
       </c>
     </row>
@@ -657,20 +657,93 @@
           <t>Всего ключевых слов</t>
         </is>
       </c>
-      <c r="B10" s="6" t="inlineStr">
-        <is>
-          <t>1 305</t>
-        </is>
-      </c>
-      <c r="C10" s="7" t="inlineStr">
-        <is>
-          <t>1 723</t>
-        </is>
-      </c>
-      <c r="D10" s="6" t="inlineStr">
-        <is>
-          <t>1 262</t>
-        </is>
+      <c r="B10" s="6">
+        <f>COUNTA('Гинекология ДоброМед'!A:A)-1</f>
+        <v/>
+      </c>
+      <c r="C10" s="7">
+        <f>COUNTA('Гугл-Топ Добро'!A:A)-1</f>
+        <v/>
+      </c>
+      <c r="D10" s="6">
+        <f>COUNTA('Гугл-Топ Довира'!A:A)-1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>в ТОП 1-3</t>
+        </is>
+      </c>
+      <c r="B11" s="6">
+        <f>COUNTIFS('Гинекология ДоброМед'!C:C,"&gt;=1",'Гинекология ДоброМед'!C:C,"&lt;=3")</f>
+        <v/>
+      </c>
+      <c r="C11" s="6">
+        <f>COUNTIFS('Гугл-Топ Добро'!C:C,"&gt;=1",'Гугл-Топ Добро'!C:C,"&lt;=3")</f>
+        <v/>
+      </c>
+      <c r="D11" s="7">
+        <f>COUNTIFS('Гугл-Топ Довира'!C:C,"&gt;=1",'Гугл-Топ Довира'!C:C,"&lt;=3")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>в ТОП 4-10</t>
+        </is>
+      </c>
+      <c r="B12" s="6">
+        <f>COUNTIFS('Гинекология ДоброМед'!C:C,"&gt;=4",'Гинекология ДоброМед'!C:C,"&lt;=10")</f>
+        <v/>
+      </c>
+      <c r="C12" s="6">
+        <f>COUNTIFS('Гугл-Топ Добро'!C:C,"&gt;=4",'Гугл-Топ Добро'!C:C,"&lt;=10")</f>
+        <v/>
+      </c>
+      <c r="D12" s="7">
+        <f>COUNTIFS('Гугл-Топ Довира'!C:C,"&gt;=4",'Гугл-Топ Довира'!C:C,"&lt;=10")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>Всего в ТОП 1-10</t>
+        </is>
+      </c>
+      <c r="B13" s="6">
+        <f>COUNTIFS('Гинекология ДоброМед'!C:C,"&gt;=1",'Гинекология ДоброМед'!C:C,"&lt;=10")</f>
+        <v/>
+      </c>
+      <c r="C13" s="6">
+        <f>COUNTIFS('Гугл-Топ Добро'!C:C,"&gt;=1",'Гугл-Топ Добро'!C:C,"&lt;=10")</f>
+        <v/>
+      </c>
+      <c r="D13" s="7">
+        <f>COUNTIFS('Гугл-Топ Довира'!C:C,"&gt;=1",'Гугл-Топ Довира'!C:C,"&lt;=10")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>в ТОП 11-20</t>
+        </is>
+      </c>
+      <c r="B14" s="6">
+        <f>COUNTIFS('Гинекология ДоброМед'!C:C,"&gt;=11",'Гинекология ДоброМед'!C:C,"&lt;=20")</f>
+        <v/>
+      </c>
+      <c r="C14" s="7">
+        <f>COUNTIFS('Гугл-Топ Добро'!C:C,"&gt;=11",'Гугл-Топ Добро'!C:C,"&lt;=20")</f>
+        <v/>
+      </c>
+      <c r="D14" s="6">
+        <f>COUNTIFS('Гугл-Топ Довира'!C:C,"&gt;=11",'Гугл-Топ Довира'!C:C,"&lt;=20")</f>
+        <v/>
       </c>
     </row>
   </sheetData>
